--- a/templates/TEMPLATE.xlsx
+++ b/templates/TEMPLATE.xlsx
@@ -71,7 +71,7 @@
   </si>
   <si>
     <t>部门编码
-DP   NO. 613</t>
+DP   NO. 623</t>
   </si>
   <si>
     <t>凭证编号
